--- a/copart_lots.xlsx
+++ b/copart_lots.xlsx
@@ -720,7 +720,7 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -888,7 +888,7 @@
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -1918,7 +1918,7 @@
         <v>34941</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>4300</v>
+        <v>6800</v>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
@@ -3115,7 +3115,7 @@
         <v>33621</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>3700</v>
+        <v>6100</v>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="T46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U46" s="6" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U47" s="3" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="T48" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U48" s="6" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U49" s="3" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="T50" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U50" s="6" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U51" s="3" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="T52" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U52" s="6" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U53" s="3" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="T54" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U54" s="6" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U55" s="3" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T56" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U56" s="6" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U57" s="3" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="T58" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U58" s="6" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U59" s="3" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="T60" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U60" s="6" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U61" s="3" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="T62" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U62" s="6" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U63" s="3" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="T64" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U64" s="6" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U65" s="3" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="T66" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U66" s="6" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U67" s="3" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="T68" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U68" s="6" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="T69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U69" s="3" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U71" s="3" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U72" s="6" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="T73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U73" s="3" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="T74" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U74" s="6" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U75" s="3" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="T76" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U76" s="6" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="T77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U77" s="3" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="T78" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U78" s="6" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="T79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U79" s="3" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="T80" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U80" s="6" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="T81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U81" s="3" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="T82" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U82" s="6" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="T83" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U83" s="3" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="T84" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U84" s="6" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="T85" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U85" s="3" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="T86" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U86" s="6" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="T87" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U87" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="T88" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U88" s="6" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="T89" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U89" s="3" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="T90" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U90" s="6" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="T91" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U91" s="3" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="T92" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U92" s="6" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="T93" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U93" s="3" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="T94" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U94" s="6" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="T95" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U95" s="3" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="T96" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U96" s="6" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="T97" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U97" s="3" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="T98" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U98" s="6" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="T99" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U99" s="3" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="T100" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U100" s="6" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="T101" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U101" s="3" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="T102" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U102" s="6" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="T103" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U103" s="3" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="T104" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U104" s="6" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="T105" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U105" s="3" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="T106" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U106" s="6" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="T107" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U107" s="3" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="T108" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U108" s="6" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="T109" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U109" s="3" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="T110" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U110" s="6" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="T111" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U111" s="3" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="T112" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U112" s="6" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="T113" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U113" s="3" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="T114" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U114" s="6" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="T115" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U115" s="3" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="T116" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U116" s="6" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="T117" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U117" s="3" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="T118" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U118" s="6" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="T119" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U119" s="3" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="T120" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U120" s="6" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="T121" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U121" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="T122" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U122" s="6" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="T123" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U123" s="3" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="T124" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U124" s="6" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="T125" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U125" s="3" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="T126" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U126" s="6" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="T127" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U127" s="3" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="T128" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U128" s="6" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="T129" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U129" s="3" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="T130" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U130" s="6" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="T131" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U131" s="3" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="T132" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U132" s="6" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="T133" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U133" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="T134" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U134" s="6" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="T135" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U135" s="3" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="T136" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U136" s="6" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="T137" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U137" s="3" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="T138" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U138" s="6" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="T139" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U139" s="3" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="T140" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U140" s="6" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="T141" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U141" s="3" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="T142" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U142" s="6" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="T143" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U143" s="3" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="T144" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U144" s="6" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="T145" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U145" s="3" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="T146" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U146" s="6" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T147" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U147" s="3" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="T148" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U148" s="6" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="T149" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U149" s="3" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="T150" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U150" s="6" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="T151" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U151" s="3" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="T152" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U152" s="6" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="T153" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U153" s="3" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="T154" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U154" s="6" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="T155" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U155" s="3" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="T156" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U156" s="6" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="T157" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U157" s="3" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="T158" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U158" s="6" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="T159" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U159" s="3" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="T160" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U160" s="6" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="T161" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U161" s="3" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="T162" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U162" s="6" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="T163" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U163" s="3" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="T164" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U164" s="6" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="T165" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U165" s="3" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="T166" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U166" s="6" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="T167" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U167" s="3" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="T168" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U168" s="6" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="T169" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U169" s="3" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="T170" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U170" s="6" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="T171" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U171" s="3" t="inlineStr">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="T172" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U172" s="6" t="inlineStr">
@@ -16270,7 +16270,7 @@
       </c>
       <c r="T173" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U173" s="3" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="T174" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U174" s="6" t="inlineStr">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="T175" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U175" s="3" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="T176" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U176" s="6" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="T177" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U177" s="3" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="T178" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U178" s="6" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="T179" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U179" s="3" t="inlineStr">
@@ -16899,7 +16899,7 @@
       </c>
       <c r="T180" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U180" s="6" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="T181" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U181" s="3" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="T182" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U182" s="6" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="T183" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U183" s="3" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="T184" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U184" s="6" t="inlineStr">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="T185" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U185" s="3" t="inlineStr">
@@ -17435,7 +17435,7 @@
       </c>
       <c r="T186" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U186" s="6" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="T187" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U187" s="3" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="T188" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U188" s="6" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="T189" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U189" s="3" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="T190" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U190" s="6" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="T191" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U191" s="3" t="inlineStr">
@@ -17977,7 +17977,7 @@
       </c>
       <c r="T192" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U192" s="6" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="T193" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U193" s="3" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="T194" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U194" s="6" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="T195" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U195" s="3" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="T196" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U196" s="6" t="inlineStr">
@@ -18428,7 +18428,7 @@
       <c r="S197" s="3" t="inlineStr"/>
       <c r="T197" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U197" s="3" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="T198" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U198" s="6" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="T199" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U199" s="3" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="T200" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U200" s="6" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="T201" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U201" s="3" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="T202" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U202" s="6" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="T203" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U203" s="3" t="inlineStr">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="T204" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U204" s="6" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="T205" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U205" s="3" t="inlineStr">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="T206" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U206" s="6" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="T207" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U207" s="3" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="T208" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U208" s="6" t="inlineStr">
@@ -19522,7 +19522,7 @@
       </c>
       <c r="T209" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U209" s="3" t="inlineStr">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="T210" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U210" s="6" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="T211" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U211" s="3" t="inlineStr">
@@ -19787,7 +19787,7 @@
       </c>
       <c r="T212" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U212" s="6" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="T213" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U213" s="3" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="T214" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U214" s="6" t="inlineStr">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="T215" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U215" s="3" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="T216" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U216" s="6" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="T217" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U217" s="3" t="inlineStr">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="T218" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U218" s="6" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="T219" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U219" s="3" t="inlineStr">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="T220" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U220" s="6" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="T221" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U221" s="3" t="inlineStr">
@@ -20685,7 +20685,7 @@
       </c>
       <c r="T222" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U222" s="6" t="inlineStr">
@@ -20776,7 +20776,7 @@
       </c>
       <c r="T223" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U223" s="3" t="inlineStr">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="T224" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U224" s="6" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="T225" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U225" s="3" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="T226" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U226" s="6" t="inlineStr">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="T227" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U227" s="3" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="T228" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U228" s="6" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="T229" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U229" s="3" t="inlineStr">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="T230" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U230" s="6" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="T231" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U231" s="3" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="T232" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U232" s="6" t="inlineStr">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="T233" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U233" s="3" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="T234" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U234" s="6" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="T235" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U235" s="3" t="inlineStr">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="T236" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U236" s="6" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="T237" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U237" s="3" t="inlineStr">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="T238" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U238" s="6" t="inlineStr">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="T239" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U239" s="3" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="T240" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U240" s="6" t="inlineStr">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="T241" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U241" s="3" t="inlineStr">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="T242" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U242" s="6" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="T243" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U243" s="3" t="inlineStr">
@@ -22711,7 +22711,7 @@
       </c>
       <c r="T244" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U244" s="6" t="inlineStr">
@@ -22798,7 +22798,7 @@
       </c>
       <c r="T245" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U245" s="3" t="inlineStr">
@@ -22889,7 +22889,7 @@
       </c>
       <c r="T246" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U246" s="6" t="inlineStr">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="T247" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U247" s="3" t="inlineStr">
@@ -23063,7 +23063,7 @@
       </c>
       <c r="T248" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U248" s="6" t="inlineStr">
@@ -23162,7 +23162,7 @@
       </c>
       <c r="T249" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U249" s="3" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="T250" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U250" s="6" t="inlineStr">
@@ -23348,7 +23348,7 @@
       </c>
       <c r="T251" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U251" s="3" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="T252" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U252" s="6" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="T253" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U253" s="3" t="inlineStr">
@@ -23633,7 +23633,7 @@
       </c>
       <c r="T254" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U254" s="6" t="inlineStr">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="T255" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U255" s="3" t="inlineStr">
@@ -23815,7 +23815,7 @@
       </c>
       <c r="T256" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U256" s="6" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="T257" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U257" s="3" t="inlineStr">
@@ -24005,7 +24005,7 @@
       </c>
       <c r="T258" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U258" s="6" t="inlineStr">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="T259" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U259" s="3" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="T260" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U260" s="6" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="T261" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U261" s="3" t="inlineStr">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="T262" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U262" s="6" t="inlineStr">
@@ -24470,7 +24470,7 @@
       </c>
       <c r="T263" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U263" s="3" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="T264" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U264" s="6" t="inlineStr">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="T265" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U265" s="3" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="T266" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U266" s="6" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="T267" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U267" s="3" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="T268" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U268" s="6" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="T269" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U269" s="3" t="inlineStr">
@@ -25067,7 +25067,7 @@
         <v>28034</v>
       </c>
       <c r="M270" s="7" t="n">
-        <v>6600</v>
+        <v>7100</v>
       </c>
       <c r="N270" s="6" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
       </c>
       <c r="T270" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U270" s="6" t="inlineStr">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="T271" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U271" s="3" t="inlineStr">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="T272" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U272" s="6" t="inlineStr">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="T273" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U273" s="3" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="T274" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U274" s="6" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="T275" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U275" s="3" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="T276" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U276" s="6" t="inlineStr">
@@ -25748,7 +25748,7 @@
       </c>
       <c r="T277" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U277" s="3" t="inlineStr">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="T278" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U278" s="6" t="inlineStr">
@@ -25930,7 +25930,7 @@
       </c>
       <c r="T279" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U279" s="3" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="T280" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U280" s="6" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="T281" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U281" s="3" t="inlineStr">
@@ -26209,7 +26209,7 @@
       </c>
       <c r="T282" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U282" s="6" t="inlineStr">
@@ -26300,7 +26300,7 @@
       </c>
       <c r="T283" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U283" s="3" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="T284" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U284" s="6" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="T285" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U285" s="3" t="inlineStr">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="T286" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U286" s="6" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="T287" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U287" s="3" t="inlineStr">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="T288" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U288" s="6" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="T289" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U289" s="3" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="T290" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U290" s="6" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="T291" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U291" s="3" t="inlineStr">
@@ -27095,7 +27095,7 @@
         <v>30084</v>
       </c>
       <c r="M292" s="7" t="n">
-        <v>275</v>
+        <v>1050</v>
       </c>
       <c r="N292" s="6" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="T292" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U292" s="6" t="inlineStr">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="T293" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U293" s="3" t="inlineStr">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="T294" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U294" s="6" t="inlineStr">
@@ -27418,7 +27418,7 @@
       </c>
       <c r="T295" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U295" s="3" t="inlineStr">
@@ -27505,7 +27505,7 @@
       </c>
       <c r="T296" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U296" s="6" t="inlineStr">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="T297" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U297" s="3" t="inlineStr">
@@ -27695,7 +27695,7 @@
       </c>
       <c r="T298" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U298" s="6" t="inlineStr">
@@ -27782,7 +27782,7 @@
       </c>
       <c r="T299" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:04:40 UTC</t>
+          <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
       <c r="U299" s="3" t="inlineStr">
